--- a/artfynd/A 29642-2022 artfynd.xlsx
+++ b/artfynd/A 29642-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29642-2022 artfynd.xlsx
+++ b/artfynd/A 29642-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4423,6 +4423,118 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122383768</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8425</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Flugmötesskogen , Flugmötesskogen , Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>580656</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6579652</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ella Axelsson Elfving</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ella Axelsson Elfving</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29642-2022 artfynd.xlsx
+++ b/artfynd/A 29642-2022 artfynd.xlsx
@@ -4428,7 +4428,7 @@
         <v>122383768</v>
       </c>
       <c r="B31" t="n">
-        <v>8425</v>
+        <v>8430</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 29642-2022 artfynd.xlsx
+++ b/artfynd/A 29642-2022 artfynd.xlsx
@@ -4443,11 +4443,6 @@
       <c r="E31" t="n">
         <v>106554</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Scolytus ratzeburgii</t>

--- a/artfynd/A 29642-2022 artfynd.xlsx
+++ b/artfynd/A 29642-2022 artfynd.xlsx
@@ -4443,6 +4443,11 @@
       <c r="E31" t="n">
         <v>106554</v>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Scolytus ratzeburgii</t>
